--- a/academias/Inglés - Estadisticos 20212.xlsx
+++ b/academias/Inglés - Estadisticos 20212.xlsx
@@ -800,25 +800,25 @@
         <v>28</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G9" s="1">
-        <v>7.14</v>
+        <v>10.71</v>
       </c>
       <c r="H9" s="1">
-        <v>92.86</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="I9" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K9" s="1">
-        <v>92.86</v>
+        <v>89.29000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1269,22 +1269,25 @@
         <v>28</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F23">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>82.14</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>17.86</v>
+      </c>
+      <c r="I23" s="2">
+        <v>7.3</v>
       </c>
       <c r="J23">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>17.86</v>
       </c>
     </row>
   </sheetData>
@@ -2351,25 +2354,25 @@
         <v>28</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G9" s="1">
-        <v>7.14</v>
+        <v>10.71</v>
       </c>
       <c r="H9" s="1">
-        <v>92.86</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="I9" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K9" s="1">
-        <v>92.86</v>
+        <v>89.29000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2820,22 +2823,25 @@
         <v>28</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F23">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>82.14</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>17.86</v>
+      </c>
+      <c r="I23" s="2">
+        <v>7.3</v>
       </c>
       <c r="J23">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>17.86</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Inglés - Estadisticos 20212.xlsx
+++ b/academias/Inglés - Estadisticos 20212.xlsx
@@ -768,22 +768,25 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>60</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.5</v>
       </c>
       <c r="J8">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -800,25 +803,25 @@
         <v>28</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F9">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>10.71</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>89.29000000000001</v>
+        <v>35.71</v>
       </c>
       <c r="I9" s="2">
         <v>8</v>
       </c>
       <c r="J9">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K9" s="1">
-        <v>89.29000000000001</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -835,22 +838,25 @@
         <v>19</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>63.16</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>36.84</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.1</v>
       </c>
       <c r="J10">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1007,25 +1013,25 @@
         <v>41</v>
       </c>
       <c r="E15">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>87.8</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>12.2</v>
+        <v>9.76</v>
       </c>
       <c r="I15" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K15" s="1">
-        <v>12.2</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1077,22 +1083,25 @@
         <v>32</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F17">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>7.9</v>
       </c>
       <c r="J17">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1109,22 +1118,25 @@
         <v>44</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F18">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>97.73</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>2.27</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7.9</v>
       </c>
       <c r="J18">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1141,22 +1153,25 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F19">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>3.7</v>
+      </c>
+      <c r="I19" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J19">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1173,22 +1188,25 @@
         <v>37</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F20">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>10.81</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J20">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1205,22 +1223,25 @@
         <v>32</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F21">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>15.63</v>
+      </c>
+      <c r="I21" s="2">
+        <v>7.8</v>
       </c>
       <c r="J21">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1237,22 +1258,25 @@
         <v>44</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F22">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>6.82</v>
+      </c>
+      <c r="I22" s="2">
+        <v>7.8</v>
       </c>
       <c r="J22">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2322,22 +2346,25 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>60</v>
+      </c>
+      <c r="I8" s="2">
+        <v>7.5</v>
       </c>
       <c r="J8">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2354,25 +2381,25 @@
         <v>28</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F9">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
-        <v>10.71</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>89.29000000000001</v>
+        <v>35.71</v>
       </c>
       <c r="I9" s="2">
         <v>8</v>
       </c>
       <c r="J9">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="K9" s="1">
-        <v>89.29000000000001</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2389,22 +2416,25 @@
         <v>19</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F10">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>63.16</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>36.84</v>
+      </c>
+      <c r="I10" s="2">
+        <v>7.1</v>
       </c>
       <c r="J10">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2561,25 +2591,25 @@
         <v>41</v>
       </c>
       <c r="E15">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>87.8</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="H15" s="1">
-        <v>12.2</v>
+        <v>9.76</v>
       </c>
       <c r="I15" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K15" s="1">
-        <v>12.2</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2631,22 +2661,25 @@
         <v>32</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F17">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>7.9</v>
       </c>
       <c r="J17">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2663,22 +2696,25 @@
         <v>44</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F18">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>97.73</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>2.27</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7.9</v>
       </c>
       <c r="J18">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2695,22 +2731,25 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F19">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>96.3</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>3.7</v>
+      </c>
+      <c r="I19" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J19">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2727,22 +2766,25 @@
         <v>37</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F20">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>89.19</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>10.81</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J20">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2759,22 +2801,25 @@
         <v>32</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F21">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>15.63</v>
+      </c>
+      <c r="I21" s="2">
+        <v>7.8</v>
       </c>
       <c r="J21">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2791,22 +2836,25 @@
         <v>44</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F22">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>6.82</v>
+      </c>
+      <c r="I22" s="2">
+        <v>7.8</v>
       </c>
       <c r="J22">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="23" spans="1:11">

--- a/academias/Inglés - Estadisticos 20212.xlsx
+++ b/academias/Inglés - Estadisticos 20212.xlsx
@@ -908,25 +908,25 @@
         <v>19</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G12" s="1">
-        <v>5.26</v>
+        <v>15.79</v>
       </c>
       <c r="H12" s="1">
-        <v>94.73999999999999</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="I12" s="2">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="J12">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K12" s="1">
-        <v>94.73999999999999</v>
+        <v>84.20999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2486,25 +2486,25 @@
         <v>19</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G12" s="1">
-        <v>5.26</v>
+        <v>15.79</v>
       </c>
       <c r="H12" s="1">
-        <v>94.73999999999999</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="I12" s="2">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="J12">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K12" s="1">
-        <v>94.73999999999999</v>
+        <v>84.20999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:11">

--- a/academias/Inglés - Estadisticos 20212.xlsx
+++ b/academias/Inglés - Estadisticos 20212.xlsx
@@ -803,25 +803,25 @@
         <v>28</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>64.29000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="H9" s="1">
-        <v>35.71</v>
+        <v>7.14</v>
       </c>
       <c r="I9" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>32.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -873,25 +873,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F11">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>38.24</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>61.76</v>
+        <v>14.71</v>
       </c>
       <c r="I11" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J11">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="K11" s="1">
-        <v>61.76</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -908,25 +908,25 @@
         <v>19</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F12">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>15.79</v>
+        <v>89.47</v>
       </c>
       <c r="H12" s="1">
-        <v>84.20999999999999</v>
+        <v>10.53</v>
       </c>
       <c r="I12" s="2">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>84.20999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2381,25 +2381,25 @@
         <v>28</v>
       </c>
       <c r="E9">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>64.29000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="H9" s="1">
-        <v>35.71</v>
+        <v>7.14</v>
       </c>
       <c r="I9" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J9">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>32.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2451,25 +2451,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F11">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>38.24</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>61.76</v>
+        <v>14.71</v>
       </c>
       <c r="I11" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J11">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="K11" s="1">
-        <v>61.76</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2486,25 +2486,25 @@
         <v>19</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F12">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>15.79</v>
+        <v>89.47</v>
       </c>
       <c r="H12" s="1">
-        <v>84.20999999999999</v>
+        <v>10.53</v>
       </c>
       <c r="I12" s="2">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>84.20999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">

--- a/academias/Inglés - Estadisticos 20212.xlsx
+++ b/academias/Inglés - Estadisticos 20212.xlsx
@@ -590,19 +590,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>83.78</v>
+        <v>83.33</v>
       </c>
       <c r="H3" s="1">
-        <v>16.22</v>
+        <v>16.67</v>
       </c>
       <c r="I3" s="2">
         <v>8</v>
@@ -768,25 +768,25 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1">
-        <v>40</v>
+        <v>53.33</v>
       </c>
       <c r="H8" s="1">
-        <v>60</v>
+        <v>46.67</v>
       </c>
       <c r="I8" s="2">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="J8">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K8" s="1">
-        <v>56.67</v>
+        <v>43.33</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -800,22 +800,22 @@
         <v>38</v>
       </c>
       <c r="D9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="I9" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -873,25 +873,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>85.29000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>14.71</v>
+        <v>11.76</v>
       </c>
       <c r="I11" s="2">
         <v>8.6</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K11" s="1">
-        <v>8.82</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -990,13 +990,13 @@
         <v>11.11</v>
       </c>
       <c r="I14" s="2">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>11.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1025,13 +1025,13 @@
         <v>9.76</v>
       </c>
       <c r="I15" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>4.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1118,25 +1118,25 @@
         <v>44</v>
       </c>
       <c r="E18">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>97.73</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
         <v>7.9</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>2.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1153,25 +1153,25 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1188,25 +1188,25 @@
         <v>37</v>
       </c>
       <c r="E20">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>89.19</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1223,25 +1223,25 @@
         <v>32</v>
       </c>
       <c r="E21">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>84.38</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1258,25 +1258,25 @@
         <v>44</v>
       </c>
       <c r="E22">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>93.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H22" s="1">
-        <v>6.82</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2">
         <v>7.8</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>6.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1380,22 +1380,25 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>78.13</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>21.88</v>
+      </c>
+      <c r="I2" s="2">
+        <v>7.8</v>
       </c>
       <c r="J2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1409,13 +1412,13 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
@@ -1424,7 +1427,7 @@
         <v>100</v>
       </c>
       <c r="J3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K3" s="1">
         <v>100</v>
@@ -1444,22 +1447,25 @@
         <v>24</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>70.83</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>29.17</v>
+      </c>
+      <c r="I4" s="2">
+        <v>6.8</v>
       </c>
       <c r="J4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1476,22 +1482,25 @@
         <v>36</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>69.44</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>30.56</v>
+      </c>
+      <c r="I5" s="2">
+        <v>7.5</v>
       </c>
       <c r="J5">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1508,22 +1517,25 @@
         <v>33</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>72.73</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>27.27</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1601,13 +1613,13 @@
         <v>38</v>
       </c>
       <c r="D9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -1616,7 +1628,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K9" s="1">
         <v>100</v>
@@ -1732,22 +1744,25 @@
         <v>36</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F13">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>91.67</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>8.33</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.2</v>
       </c>
       <c r="J13">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1764,22 +1779,25 @@
         <v>36</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F14">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>58.33</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>41.67</v>
+      </c>
+      <c r="I14" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J14">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1796,22 +1814,25 @@
         <v>41</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F15">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>9.76</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>90.23999999999999</v>
+      </c>
+      <c r="I15" s="2">
+        <v>7.5</v>
       </c>
       <c r="J15">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>90.23999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1828,22 +1849,25 @@
         <v>16</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F16">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>8.4</v>
       </c>
       <c r="J16">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1860,22 +1884,25 @@
         <v>32</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F17">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>8.6</v>
       </c>
       <c r="J17">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1892,22 +1919,25 @@
         <v>44</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F18">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <v>8.5</v>
       </c>
       <c r="J18">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1924,22 +1954,25 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F19">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>8.6</v>
       </c>
       <c r="J19">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1956,22 +1989,25 @@
         <v>37</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F20">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I20" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J20">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1988,22 +2024,25 @@
         <v>32</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F21">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>8.1</v>
       </c>
       <c r="J21">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2020,22 +2059,25 @@
         <v>44</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F22">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
+        <v>7.8</v>
       </c>
       <c r="J22">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2136,19 +2178,19 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>65.63</v>
+        <v>78.13</v>
       </c>
       <c r="H2" s="1">
-        <v>34.38</v>
+        <v>21.88</v>
       </c>
       <c r="I2" s="2">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2168,19 +2210,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>6</v>
       </c>
       <c r="G3" s="1">
-        <v>83.78</v>
+        <v>83.33</v>
       </c>
       <c r="H3" s="1">
-        <v>16.22</v>
+        <v>16.67</v>
       </c>
       <c r="I3" s="2">
         <v>8</v>
@@ -2206,16 +2248,16 @@
         <v>24</v>
       </c>
       <c r="E4">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1">
-        <v>66.67</v>
+        <v>70.83</v>
       </c>
       <c r="H4" s="1">
-        <v>33.33</v>
+        <v>29.17</v>
       </c>
       <c r="I4" s="2">
         <v>6.8</v>
@@ -2241,19 +2283,19 @@
         <v>36</v>
       </c>
       <c r="E5">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G5" s="1">
-        <v>75</v>
+        <v>69.44</v>
       </c>
       <c r="H5" s="1">
-        <v>25</v>
+        <v>30.56</v>
       </c>
       <c r="I5" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2346,25 +2388,25 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G8" s="1">
-        <v>40</v>
+        <v>53.33</v>
       </c>
       <c r="H8" s="1">
-        <v>60</v>
+        <v>46.67</v>
       </c>
       <c r="I8" s="2">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="J8">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K8" s="1">
-        <v>56.67</v>
+        <v>43.33</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2378,22 +2420,22 @@
         <v>38</v>
       </c>
       <c r="D9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9">
         <v>2</v>
       </c>
       <c r="G9" s="1">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="I9" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2451,25 +2493,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>85.29000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>14.71</v>
+        <v>11.76</v>
       </c>
       <c r="I11" s="2">
         <v>8.6</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K11" s="1">
-        <v>8.82</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2533,7 +2575,7 @@
         <v>8.33</v>
       </c>
       <c r="I13" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2568,13 +2610,13 @@
         <v>11.11</v>
       </c>
       <c r="I14" s="2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>11.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2603,13 +2645,13 @@
         <v>9.76</v>
       </c>
       <c r="I15" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>4.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2638,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2673,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2696,25 +2738,25 @@
         <v>44</v>
       </c>
       <c r="E18">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>97.73</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>2.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2731,25 +2773,25 @@
         <v>27</v>
       </c>
       <c r="E19">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>96.3</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2766,25 +2808,25 @@
         <v>37</v>
       </c>
       <c r="E20">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>89.19</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J20">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>10.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2801,25 +2843,25 @@
         <v>32</v>
       </c>
       <c r="E21">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>84.38</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2836,25 +2878,25 @@
         <v>44</v>
       </c>
       <c r="E22">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>93.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H22" s="1">
-        <v>6.82</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>6.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">

--- a/academias/Inglés - Estadisticos 20212.xlsx
+++ b/academias/Inglés - Estadisticos 20212.xlsx
@@ -1293,25 +1293,25 @@
         <v>28</v>
       </c>
       <c r="E23">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" s="1">
-        <v>82.14</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>17.86</v>
+        <v>14.29</v>
       </c>
       <c r="I23" s="2">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K23" s="1">
-        <v>17.86</v>
+        <v>10.71</v>
       </c>
     </row>
   </sheetData>
@@ -1415,22 +1415,25 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>88.89</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>11.11</v>
+      </c>
+      <c r="I3" s="2">
+        <v>8.6</v>
       </c>
       <c r="J3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1552,22 +1555,25 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>71.88</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>28.13</v>
+      </c>
+      <c r="I7" s="2">
+        <v>7.3</v>
       </c>
       <c r="J7">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1779,25 +1785,25 @@
         <v>36</v>
       </c>
       <c r="E14">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F14">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G14" s="1">
-        <v>58.33</v>
+        <v>77.78</v>
       </c>
       <c r="H14" s="1">
-        <v>41.67</v>
+        <v>22.22</v>
       </c>
       <c r="I14" s="2">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J14">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K14" s="1">
-        <v>41.67</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1814,25 +1820,25 @@
         <v>41</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="F15">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="G15" s="1">
-        <v>9.76</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>90.23999999999999</v>
+        <v>31.71</v>
       </c>
       <c r="I15" s="2">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="J15">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="K15" s="1">
-        <v>90.23999999999999</v>
+        <v>19.51</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2094,22 +2100,25 @@
         <v>28</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F23">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I23" s="2">
+        <v>5.8</v>
       </c>
       <c r="J23">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>14.29</v>
       </c>
     </row>
   </sheetData>
@@ -2213,19 +2222,19 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G3" s="1">
-        <v>83.33</v>
+        <v>88.89</v>
       </c>
       <c r="H3" s="1">
-        <v>16.67</v>
+        <v>11.11</v>
       </c>
       <c r="I3" s="2">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2353,19 +2362,19 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G7" s="1">
-        <v>81.25</v>
+        <v>71.88</v>
       </c>
       <c r="H7" s="1">
-        <v>18.75</v>
+        <v>28.13</v>
       </c>
       <c r="I7" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2598,16 +2607,16 @@
         <v>36</v>
       </c>
       <c r="E14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>88.89</v>
+        <v>94.44</v>
       </c>
       <c r="H14" s="1">
-        <v>11.11</v>
+        <v>5.56</v>
       </c>
       <c r="I14" s="2">
         <v>7.8</v>
@@ -2633,19 +2642,19 @@
         <v>41</v>
       </c>
       <c r="E15">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G15" s="1">
-        <v>90.23999999999999</v>
+        <v>85.37</v>
       </c>
       <c r="H15" s="1">
-        <v>9.76</v>
+        <v>14.63</v>
       </c>
       <c r="I15" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2913,25 +2922,25 @@
         <v>28</v>
       </c>
       <c r="E23">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" s="1">
-        <v>82.14</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>17.86</v>
+        <v>21.43</v>
       </c>
       <c r="I23" s="2">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="J23">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K23" s="1">
-        <v>17.86</v>
+        <v>10.71</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Inglés - Estadisticos 20212.xlsx
+++ b/academias/Inglés - Estadisticos 20212.xlsx
@@ -1785,25 +1785,25 @@
         <v>36</v>
       </c>
       <c r="E14">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G14" s="1">
-        <v>77.78</v>
+        <v>94.44</v>
       </c>
       <c r="H14" s="1">
-        <v>22.22</v>
+        <v>5.56</v>
       </c>
       <c r="I14" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>19.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">

--- a/academias/Inglés - Estadisticos 20212.xlsx
+++ b/academias/Inglés - Estadisticos 20212.xlsx
@@ -768,25 +768,25 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1">
-        <v>53.33</v>
+        <v>66.67</v>
       </c>
       <c r="H8" s="1">
-        <v>46.67</v>
+        <v>33.33</v>
       </c>
       <c r="I8" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K8" s="1">
-        <v>43.33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -873,25 +873,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>88.23999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>11.76</v>
+        <v>8.82</v>
       </c>
       <c r="I11" s="2">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1590,22 +1590,25 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>43.33</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>56.67</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J8">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1622,22 +1625,25 @@
         <v>29</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F9">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>79.31</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>20.69</v>
+      </c>
+      <c r="I9" s="2">
+        <v>8.6</v>
       </c>
       <c r="J9">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>20.69</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1654,22 +1660,25 @@
         <v>19</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F10">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>57.89</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>42.11</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.5</v>
       </c>
       <c r="J10">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1686,22 +1695,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F11">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>79.41</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>20.59</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8.9</v>
       </c>
       <c r="J11">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1718,22 +1730,25 @@
         <v>19</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F12">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>78.95</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>21.05</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8.699999999999999</v>
       </c>
       <c r="J12">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1820,25 +1835,25 @@
         <v>41</v>
       </c>
       <c r="E15">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F15">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G15" s="1">
-        <v>68.29000000000001</v>
+        <v>75.61</v>
       </c>
       <c r="H15" s="1">
-        <v>31.71</v>
+        <v>24.39</v>
       </c>
       <c r="I15" s="2">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="J15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K15" s="1">
-        <v>19.51</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2397,25 +2412,25 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G8" s="1">
-        <v>53.33</v>
+        <v>70</v>
       </c>
       <c r="H8" s="1">
-        <v>46.67</v>
+        <v>30</v>
       </c>
       <c r="I8" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J8">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K8" s="1">
-        <v>43.33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2444,7 +2459,7 @@
         <v>6.9</v>
       </c>
       <c r="I9" s="2">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2467,19 +2482,19 @@
         <v>19</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>63.16</v>
+        <v>68.42</v>
       </c>
       <c r="H10" s="1">
-        <v>36.84</v>
+        <v>31.58</v>
       </c>
       <c r="I10" s="2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2502,25 +2517,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H11" s="1">
-        <v>11.76</v>
+        <v>5.88</v>
       </c>
       <c r="I11" s="2">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" s="1">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2537,19 +2552,19 @@
         <v>19</v>
       </c>
       <c r="E12">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
-        <v>89.47</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>10.53</v>
+        <v>5.26</v>
       </c>
       <c r="I12" s="2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2654,7 +2669,7 @@
         <v>14.63</v>
       </c>
       <c r="I15" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J15">
         <v>0</v>

--- a/academias/Inglés - Estadisticos 20212.xlsx
+++ b/academias/Inglés - Estadisticos 20212.xlsx
@@ -768,25 +768,25 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>66.67</v>
+        <v>83.33</v>
       </c>
       <c r="H8" s="1">
-        <v>33.33</v>
+        <v>16.67</v>
       </c>
       <c r="I8" s="2">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="J8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -885,13 +885,13 @@
         <v>8.82</v>
       </c>
       <c r="I11" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1293,25 +1293,25 @@
         <v>28</v>
       </c>
       <c r="E23">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G23" s="1">
-        <v>85.70999999999999</v>
+        <v>92.86</v>
       </c>
       <c r="H23" s="1">
-        <v>14.29</v>
+        <v>7.14</v>
       </c>
       <c r="I23" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>10.71</v>
+        <v>3.57</v>
       </c>
     </row>
   </sheetData>
@@ -1590,25 +1590,25 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>43.33</v>
+        <v>83.33</v>
       </c>
       <c r="H8" s="1">
-        <v>56.67</v>
+        <v>16.67</v>
       </c>
       <c r="I8" s="2">
-        <v>8.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="J8">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>56.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1625,25 +1625,25 @@
         <v>29</v>
       </c>
       <c r="E9">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>79.31</v>
+        <v>89.66</v>
       </c>
       <c r="H9" s="1">
-        <v>20.69</v>
+        <v>10.34</v>
       </c>
       <c r="I9" s="2">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>20.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1660,25 +1660,25 @@
         <v>19</v>
       </c>
       <c r="E10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>57.89</v>
+        <v>68.42</v>
       </c>
       <c r="H10" s="1">
-        <v>42.11</v>
+        <v>31.58</v>
       </c>
       <c r="I10" s="2">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="J10">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>42.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1695,25 +1695,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>79.41</v>
+        <v>94.12</v>
       </c>
       <c r="H11" s="1">
-        <v>20.59</v>
+        <v>5.88</v>
       </c>
       <c r="I11" s="2">
-        <v>8.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J11">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>20.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1730,25 +1730,25 @@
         <v>19</v>
       </c>
       <c r="E12">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>78.95</v>
+        <v>89.47</v>
       </c>
       <c r="H12" s="1">
-        <v>21.05</v>
+        <v>10.53</v>
       </c>
       <c r="I12" s="2">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>21.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1777,13 +1777,13 @@
         <v>8.33</v>
       </c>
       <c r="I13" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1835,25 +1835,25 @@
         <v>41</v>
       </c>
       <c r="E15">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G15" s="1">
-        <v>75.61</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>24.39</v>
+        <v>17.07</v>
       </c>
       <c r="I15" s="2">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>9.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2115,25 +2115,25 @@
         <v>28</v>
       </c>
       <c r="E23">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F23">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G23" s="1">
-        <v>75</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>25</v>
+        <v>14.29</v>
       </c>
       <c r="I23" s="2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>14.29</v>
+        <v>3.57</v>
       </c>
     </row>
   </sheetData>
@@ -2202,19 +2202,19 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>78.13</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>21.88</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2237,19 +2237,19 @@
         <v>36</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1">
-        <v>88.89</v>
+        <v>94.44</v>
       </c>
       <c r="H3" s="1">
-        <v>11.11</v>
+        <v>5.56</v>
       </c>
       <c r="I3" s="2">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2272,19 +2272,19 @@
         <v>24</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G4" s="1">
-        <v>70.83</v>
+        <v>91.67</v>
       </c>
       <c r="H4" s="1">
-        <v>29.17</v>
+        <v>8.33</v>
       </c>
       <c r="I4" s="2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2307,19 +2307,19 @@
         <v>36</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G5" s="1">
-        <v>69.44</v>
+        <v>83.33</v>
       </c>
       <c r="H5" s="1">
-        <v>30.56</v>
+        <v>16.67</v>
       </c>
       <c r="I5" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2342,19 +2342,19 @@
         <v>33</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>72.73</v>
+        <v>93.94</v>
       </c>
       <c r="H6" s="1">
-        <v>27.27</v>
+        <v>6.06</v>
       </c>
       <c r="I6" s="2">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2377,19 +2377,19 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>71.88</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>28.13</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2412,25 +2412,25 @@
         <v>30</v>
       </c>
       <c r="E8">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F8">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>70</v>
+        <v>83.33</v>
       </c>
       <c r="H8" s="1">
-        <v>30</v>
+        <v>16.67</v>
       </c>
       <c r="I8" s="2">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="J8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2447,19 +2447,19 @@
         <v>29</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
-        <v>93.09999999999999</v>
+        <v>89.66</v>
       </c>
       <c r="H9" s="1">
-        <v>6.9</v>
+        <v>10.34</v>
       </c>
       <c r="I9" s="2">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2482,19 +2482,19 @@
         <v>19</v>
       </c>
       <c r="E10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>68.42</v>
+        <v>78.95</v>
       </c>
       <c r="H10" s="1">
-        <v>31.58</v>
+        <v>21.05</v>
       </c>
       <c r="I10" s="2">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -2517,25 +2517,25 @@
         <v>34</v>
       </c>
       <c r="E11">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>94.12</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2552,19 +2552,19 @@
         <v>19</v>
       </c>
       <c r="E12">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="1">
-        <v>94.73999999999999</v>
+        <v>89.47</v>
       </c>
       <c r="H12" s="1">
-        <v>5.26</v>
+        <v>10.53</v>
       </c>
       <c r="I12" s="2">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2587,19 +2587,19 @@
         <v>36</v>
       </c>
       <c r="E13">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
-        <v>91.67</v>
+        <v>94.44</v>
       </c>
       <c r="H13" s="1">
-        <v>8.33</v>
+        <v>5.56</v>
       </c>
       <c r="I13" s="2">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2622,16 +2622,16 @@
         <v>36</v>
       </c>
       <c r="E14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="1">
-        <v>94.44</v>
+        <v>97.22</v>
       </c>
       <c r="H14" s="1">
-        <v>5.56</v>
+        <v>2.78</v>
       </c>
       <c r="I14" s="2">
         <v>7.8</v>
@@ -2669,7 +2669,7 @@
         <v>14.63</v>
       </c>
       <c r="I15" s="2">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2704,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2937,25 +2937,25 @@
         <v>28</v>
       </c>
       <c r="E23">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G23" s="1">
-        <v>78.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H23" s="1">
-        <v>21.43</v>
+        <v>14.29</v>
       </c>
       <c r="I23" s="2">
         <v>6.7</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K23" s="1">
-        <v>10.71</v>
+        <v>3.57</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Inglés - Estadisticos 20212.xlsx
+++ b/academias/Inglés - Estadisticos 20212.xlsx
@@ -2844,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="J21">
         <v>0</v>

--- a/academias/Inglés - Estadisticos 20212.xlsx
+++ b/academias/Inglés - Estadisticos 20212.xlsx
@@ -1308,10 +1308,10 @@
         <v>7</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>3.57</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2127,13 +2127,13 @@
         <v>14.29</v>
       </c>
       <c r="I23" s="2">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>3.57</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2424,7 +2424,7 @@
         <v>16.67</v>
       </c>
       <c r="I8" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2739,7 +2739,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2774,7 +2774,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2809,7 +2809,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -2937,25 +2937,25 @@
         <v>28</v>
       </c>
       <c r="E23">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>85.70999999999999</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H23" s="1">
-        <v>14.29</v>
+        <v>3.57</v>
       </c>
       <c r="I23" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>3.57</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
